--- a/artfynd/S 2786-2023 artfynd.xlsx
+++ b/artfynd/S 2786-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/617088</t>
         </is>
       </c>
     </row>
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121676022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121676031</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121676019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121676046</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119568</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119571</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,6 +1581,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119572</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119575</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119576</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1876,6 +1931,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119579</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,6 +2046,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119584</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2096,6 +2161,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119585</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2209,6 +2279,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119588</t>
         </is>
       </c>
     </row>
@@ -2318,6 +2393,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121676044</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2422,6 +2502,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3566755</t>
         </is>
       </c>
     </row>
@@ -2531,6 +2616,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121676030</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2638,6 +2728,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121676053</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2745,6 +2840,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121676032</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2852,6 +2952,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121676036</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2959,8 +3064,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121676038</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>